--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -10830,31 +10830,6 @@
     </a:ln>
   </spPr>
 </chartSpace>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Acta de Obra" sheetId="1" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acta de Obra" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy"/>
@@ -22,6 +23,7 @@
     <numFmt numFmtId="168" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="169" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="170" formatCode="&quot;$&quot;\ #,##0.00"/>
+    <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
   </numFmts>
   <fonts count="165">
     <font>
@@ -6668,7 +6670,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1453">
+  <cellXfs count="1455">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -10267,6 +10269,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="277" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="40" fillId="21" borderId="417" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="123" fillId="54" borderId="182" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="123" fillId="54" borderId="185" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10399,440 +10407,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO" sz="1800" b="1" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:rPr>
-              <a:t>Costo directo por capítulo (COP)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Resumen!$C$11</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Valor (COP)</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="4F81BD"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Arial"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t>None</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="1"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Resumen!$A$12:$A$25</f>
-              <strCache>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>1</v>
-                </pt>
-                <pt idx="1">
-                  <v>2</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>4</v>
-                </pt>
-                <pt idx="4">
-                  <v>5</v>
-                </pt>
-                <pt idx="5">
-                  <v>6</v>
-                </pt>
-                <pt idx="6">
-                  <v>7</v>
-                </pt>
-                <pt idx="7">
-                  <v>8</v>
-                </pt>
-                <pt idx="8">
-                  <v>9</v>
-                </pt>
-                <pt idx="9">
-                  <v>10</v>
-                </pt>
-                <pt idx="10">
-                  <v>11</v>
-                </pt>
-                <pt idx="11">
-                  <v>12</v>
-                </pt>
-                <pt idx="12">
-                  <v>13</v>
-                </pt>
-                <pt idx="13">
-                  <v>14</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Resumen!$C$12:$C$25</f>
-              <numCache>
-                <formatCode>"$ "#,##0</formatCode>
-                <ptCount val="14"/>
-                <pt idx="0">
-                  <v>0</v>
-                </pt>
-                <pt idx="1">
-                  <v>0</v>
-                </pt>
-                <pt idx="2">
-                  <v>0</v>
-                </pt>
-                <pt idx="3">
-                  <v>0</v>
-                </pt>
-                <pt idx="4">
-                  <v>0</v>
-                </pt>
-                <pt idx="5">
-                  <v>0</v>
-                </pt>
-                <pt idx="6">
-                  <v>0</v>
-                </pt>
-                <pt idx="7">
-                  <v>0</v>
-                </pt>
-                <pt idx="8">
-                  <v>0</v>
-                </pt>
-                <pt idx="9">
-                  <v>0</v>
-                </pt>
-                <pt idx="10">
-                  <v>0</v>
-                </pt>
-                <pt idx="11">
-                  <v>0</v>
-                </pt>
-                <pt idx="12">
-                  <v>0</v>
-                </pt>
-                <pt idx="13">
-                  <v>0</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="150"/>
-        <axId val="50050775"/>
-        <axId val="41416401"/>
-      </barChart>
-      <catAx>
-        <axId val="50050775"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>Capítulo</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="General" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="41416401"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="41416401"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-              <a:solidFill>
-                <a:srgbClr val="878787"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-CO" sz="1000" b="1" strike="noStrike" spc="-1">
-                    <a:solidFill>
-                      <a:srgbClr val="000000"/>
-                    </a:solidFill>
-                    <a:latin typeface="Calibri"/>
-                  </a:rPr>
-                  <a:t>COP</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-        </title>
-        <numFmt formatCode="&quot;$ &quot;#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-            <a:solidFill>
-              <a:srgbClr val="878787"/>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-                <a:solidFill>
-                  <a:srgbClr val="000000"/>
-                </a:solidFill>
-                <a:latin typeface="Calibri"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t>None</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </txPr>
-        <crossAx val="50050775"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="0">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t>None</a:t>
-          </a:r>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:srgbClr val="FFFFFF"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9360">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -11054,7 +10629,7 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
@@ -11845,7 +11420,7 @@
       <c r="B36" s="839" t="n"/>
       <c r="C36" s="839" t="n"/>
       <c r="D36" s="839" t="n"/>
-      <c r="E36" s="1385" t="n"/>
+      <c r="E36" s="1453" t="n"/>
       <c r="F36" s="846" t="inlineStr">
         <is>
           <t>Valor actas anteriores</t>
@@ -11880,7 +11455,7 @@
       <c r="B37" s="826" t="n"/>
       <c r="C37" s="826" t="n"/>
       <c r="D37" s="826" t="n"/>
-      <c r="E37" s="1388">
+      <c r="E37" s="1454">
         <f>IFERROR((H36+K36)/E36,0)</f>
         <v/>
       </c>
@@ -12973,6 +12548,5 @@
     <firstFooter/>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -14,7 +14,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="_-&quot;$ &quot;* #,##0.00_-;&quot;-$ &quot;* #,##0.00_-;_-&quot;$ &quot;* \-??_-;_-@_-"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;\ #,##0.00"/>
@@ -23,8 +23,9 @@
     <numFmt numFmtId="169" formatCode="&quot;$ &quot;#,##0"/>
     <numFmt numFmtId="170" formatCode="\$\ #,##0.00"/>
     <numFmt numFmtId="171" formatCode="$ #,##0.00"/>
+    <numFmt numFmtId="172" formatCode="$ #,##0"/>
   </numFmts>
-  <fonts count="168">
+  <fonts count="170">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -1227,6 +1228,15 @@
     <font>
       <name val="Calibri"/>
       <color rgb="FF8A8F99"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="008A8F99"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -6573,7 +6583,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1307">
+  <cellXfs count="1310">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9797,6 +9807,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="38" fillId="4" borderId="77" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="168" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -10019,7 +10036,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
@@ -10215,7 +10232,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10306,7 +10323,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="es-CO"/>
           </a:p>
@@ -10339,7 +10356,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="es-CO"/>
         </a:p>
@@ -11128,8 +11145,16 @@
           <t>Observación</t>
         </is>
       </c>
-      <c r="M25" s="831" t="n"/>
-      <c r="N25" s="831" t="n"/>
+      <c r="M25" s="830" t="inlineStr">
+        <is>
+          <t>Precio Unit.</t>
+        </is>
+      </c>
+      <c r="N25" s="830" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="18" customHeight="1" s="1223">
       <c r="A26" s="263" t="n"/>
@@ -11153,8 +11178,11 @@
         <v/>
       </c>
       <c r="L26" s="851" t="n"/>
-      <c r="M26" s="852" t="n"/>
-      <c r="N26" s="853" t="n"/>
+      <c r="M26" s="1309" t="n"/>
+      <c r="N26" s="1309">
+        <f>IFERROR(H26*M26,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="18" customHeight="1" s="1223">
       <c r="A27" s="823" t="n"/>
@@ -11178,8 +11206,11 @@
         <v/>
       </c>
       <c r="L27" s="814" t="n"/>
-      <c r="M27" s="815" t="n"/>
-      <c r="N27" s="812" t="n"/>
+      <c r="M27" s="1309" t="n"/>
+      <c r="N27" s="1309">
+        <f>IFERROR(H27*M27,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="18" customHeight="1" s="1223">
       <c r="A28" s="823" t="n"/>
@@ -11203,8 +11234,11 @@
         <v/>
       </c>
       <c r="L28" s="814" t="n"/>
-      <c r="M28" s="815" t="n"/>
-      <c r="N28" s="812" t="n"/>
+      <c r="M28" s="1309" t="n"/>
+      <c r="N28" s="1309">
+        <f>IFERROR(H28*M28,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="18" customHeight="1" s="1223">
       <c r="A29" s="823" t="n"/>
@@ -11228,8 +11262,11 @@
         <v/>
       </c>
       <c r="L29" s="814" t="n"/>
-      <c r="M29" s="815" t="n"/>
-      <c r="N29" s="812" t="n"/>
+      <c r="M29" s="1309" t="n"/>
+      <c r="N29" s="1309">
+        <f>IFERROR(H29*M29,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="18" customHeight="1" s="1223">
       <c r="A30" s="823" t="n"/>
@@ -11253,8 +11290,11 @@
         <v/>
       </c>
       <c r="L30" s="814" t="n"/>
-      <c r="M30" s="815" t="n"/>
-      <c r="N30" s="812" t="n"/>
+      <c r="M30" s="1309" t="n"/>
+      <c r="N30" s="1309">
+        <f>IFERROR(H30*M30,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="18" customHeight="1" s="1223">
       <c r="A31" s="823" t="n"/>
@@ -11278,8 +11318,11 @@
         <v/>
       </c>
       <c r="L31" s="814" t="n"/>
-      <c r="M31" s="815" t="n"/>
-      <c r="N31" s="812" t="n"/>
+      <c r="M31" s="1309" t="n"/>
+      <c r="N31" s="1309">
+        <f>IFERROR(H31*M31,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1" s="1223">
       <c r="A32" s="823" t="n"/>
@@ -11303,8 +11346,11 @@
         <v/>
       </c>
       <c r="L32" s="814" t="n"/>
-      <c r="M32" s="815" t="n"/>
-      <c r="N32" s="812" t="n"/>
+      <c r="M32" s="1309" t="n"/>
+      <c r="N32" s="1309">
+        <f>IFERROR(H32*M32,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1" s="1223">
       <c r="A33" s="823" t="n"/>
@@ -11328,8 +11374,11 @@
         <v/>
       </c>
       <c r="L33" s="814" t="n"/>
-      <c r="M33" s="815" t="n"/>
-      <c r="N33" s="812" t="n"/>
+      <c r="M33" s="1309" t="n"/>
+      <c r="N33" s="1309">
+        <f>IFERROR(H33*M33,0)</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1" s="1223" thickBot="1">
       <c r="A34" s="214" t="n"/>
@@ -11390,7 +11439,10 @@
         </is>
       </c>
       <c r="J36" s="815" t="n"/>
-      <c r="K36" s="511" t="n"/>
+      <c r="K36" s="511">
+        <f>SUM(N26:N33)</f>
+        <v/>
+      </c>
       <c r="L36" s="889" t="inlineStr">
         <is>
           <t>Saldo contractual</t>
@@ -12298,10 +12350,9 @@
     <row r="90" ht="18" customHeight="1" s="1223"/>
     <row r="91" ht="18" customHeight="1" s="1223"/>
   </sheetData>
-  <mergeCells count="140">
+  <mergeCells count="131">
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="K49:L49"/>
-    <mergeCell ref="L33:N33"/>
     <mergeCell ref="M75:N78"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="L42:N42"/>
@@ -12310,7 +12361,6 @@
     <mergeCell ref="C40:E40"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="G40:J40"/>
-    <mergeCell ref="L25:N25"/>
     <mergeCell ref="A75:D78"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="K50:L50"/>
@@ -12324,7 +12374,6 @@
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="C42:E42"/>
     <mergeCell ref="G20:H20"/>
-    <mergeCell ref="L32:N32"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="J12:N12"/>
     <mergeCell ref="L54:N66"/>
@@ -12335,7 +12384,6 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A86:N87"/>
     <mergeCell ref="J13:N13"/>
-    <mergeCell ref="L26:N26"/>
     <mergeCell ref="K21:L21"/>
     <mergeCell ref="E46:G46"/>
     <mergeCell ref="K51:L51"/>
@@ -12357,7 +12405,6 @@
     <mergeCell ref="C14:H14"/>
     <mergeCell ref="B31:D31"/>
     <mergeCell ref="B46:D46"/>
-    <mergeCell ref="L28:N28"/>
     <mergeCell ref="A74:D74"/>
     <mergeCell ref="B48:D48"/>
     <mergeCell ref="H46:J46"/>
@@ -12387,7 +12434,6 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="I54:K66"/>
     <mergeCell ref="C20:F20"/>
-    <mergeCell ref="L27:N27"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="B25:D25"/>
@@ -12402,18 +12448,15 @@
     <mergeCell ref="A44:N44"/>
     <mergeCell ref="H49:J49"/>
     <mergeCell ref="C41:E41"/>
-    <mergeCell ref="L30:N30"/>
     <mergeCell ref="A73:N73"/>
     <mergeCell ref="I36:J36"/>
     <mergeCell ref="L37:M37"/>
     <mergeCell ref="C12:H12"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="G41:J41"/>
-    <mergeCell ref="L29:N29"/>
     <mergeCell ref="K20:L20"/>
     <mergeCell ref="E49:G49"/>
     <mergeCell ref="M20:N20"/>
-    <mergeCell ref="L31:N31"/>
     <mergeCell ref="I22:J22"/>
     <mergeCell ref="K22:L22"/>
     <mergeCell ref="L6:N6"/>

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -6583,7 +6583,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1310">
+  <cellXfs count="1311">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9814,6 +9814,9 @@
     </xf>
     <xf numFmtId="0" fontId="169" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="172" fontId="127" fillId="55" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11122,37 +11125,37 @@
       </c>
       <c r="H25" s="830" t="inlineStr">
         <is>
+          <t>Precio unitario</t>
+        </is>
+      </c>
+      <c r="I25" s="830" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="J25" s="830" t="inlineStr">
+        <is>
           <t>Cant. acta</t>
         </is>
       </c>
-      <c r="I25" s="830" t="inlineStr">
+      <c r="K25" s="830" t="inlineStr">
         <is>
           <t>Cant. acumulada</t>
         </is>
       </c>
-      <c r="J25" s="830" t="inlineStr">
+      <c r="L25" s="830" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="K25" s="830" t="inlineStr">
+      <c r="M25" s="830" t="inlineStr">
         <is>
           <t>% ejecución</t>
         </is>
       </c>
-      <c r="L25" s="830" t="inlineStr">
+      <c r="N25" s="830" t="inlineStr">
         <is>
           <t>Observación</t>
-        </is>
-      </c>
-      <c r="M25" s="830" t="inlineStr">
-        <is>
-          <t>Precio Unit.</t>
-        </is>
-      </c>
-      <c r="N25" s="830" t="inlineStr">
-        <is>
-          <t>Valor</t>
         </is>
       </c>
     </row>
@@ -11164,25 +11167,25 @@
       <c r="E26" s="392" t="n"/>
       <c r="F26" s="393" t="n"/>
       <c r="G26" s="393" t="n"/>
-      <c r="H26" s="393" t="n"/>
-      <c r="I26" s="215">
-        <f>IF(A26="","",G26+H26)</f>
+      <c r="H26" s="1310" t="n"/>
+      <c r="I26" s="1310">
+        <f>IFERROR(J26*H26,0)</f>
         <v/>
       </c>
-      <c r="J26" s="215">
-        <f>IF(F26="","",MAX(0,F26-I26))</f>
+      <c r="J26" s="393" t="n"/>
+      <c r="K26" s="215">
+        <f>IF(A26="","",G26+J26)</f>
         <v/>
       </c>
-      <c r="K26" s="508">
-        <f>IF(OR(F26="",F26=0),"",I26/F26)</f>
+      <c r="L26" s="215">
+        <f>IF(F26="","",MAX(0,F26-K26))</f>
         <v/>
       </c>
-      <c r="L26" s="851" t="n"/>
-      <c r="M26" s="1309" t="n"/>
-      <c r="N26" s="1309">
-        <f>IFERROR(H26*M26,0)</f>
+      <c r="M26" s="508">
+        <f>IF(OR(F26="",F26=0),"",K26/F26)</f>
         <v/>
       </c>
+      <c r="N26" s="851" t="n"/>
     </row>
     <row r="27" ht="18" customHeight="1" s="1223">
       <c r="A27" s="823" t="n"/>
@@ -11192,25 +11195,25 @@
       <c r="E27" s="848" t="n"/>
       <c r="F27" s="394" t="n"/>
       <c r="G27" s="394" t="n"/>
-      <c r="H27" s="394" t="n"/>
-      <c r="I27" s="216">
-        <f>IF(A27="","",G27+H27)</f>
+      <c r="H27" s="1310" t="n"/>
+      <c r="I27" s="1310">
+        <f>IFERROR(J27*H27,0)</f>
         <v/>
       </c>
-      <c r="J27" s="216">
-        <f>IF(F27="","",MAX(0,F27-I27))</f>
+      <c r="J27" s="394" t="n"/>
+      <c r="K27" s="216">
+        <f>IF(A27="","",G27+J27)</f>
         <v/>
       </c>
-      <c r="K27" s="509">
-        <f>IF(OR(F27="",F27=0),"",I27/F27)</f>
+      <c r="L27" s="216">
+        <f>IF(F27="","",MAX(0,F27-K27))</f>
         <v/>
       </c>
-      <c r="L27" s="814" t="n"/>
-      <c r="M27" s="1309" t="n"/>
-      <c r="N27" s="1309">
-        <f>IFERROR(H27*M27,0)</f>
+      <c r="M27" s="509">
+        <f>IF(OR(F27="",F27=0),"",K27/F27)</f>
         <v/>
       </c>
+      <c r="N27" s="851" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="1223">
       <c r="A28" s="823" t="n"/>
@@ -11220,25 +11223,25 @@
       <c r="E28" s="848" t="n"/>
       <c r="F28" s="394" t="n"/>
       <c r="G28" s="394" t="n"/>
-      <c r="H28" s="394" t="n"/>
-      <c r="I28" s="216">
-        <f>IF(A28="","",G28+H28)</f>
+      <c r="H28" s="1310" t="n"/>
+      <c r="I28" s="1310">
+        <f>IFERROR(J28*H28,0)</f>
         <v/>
       </c>
-      <c r="J28" s="216">
-        <f>IF(F28="","",MAX(0,F28-I28))</f>
+      <c r="J28" s="394" t="n"/>
+      <c r="K28" s="216">
+        <f>IF(A28="","",G28+J28)</f>
         <v/>
       </c>
-      <c r="K28" s="509">
-        <f>IF(OR(F28="",F28=0),"",I28/F28)</f>
+      <c r="L28" s="216">
+        <f>IF(F28="","",MAX(0,F28-K28))</f>
         <v/>
       </c>
-      <c r="L28" s="814" t="n"/>
-      <c r="M28" s="1309" t="n"/>
-      <c r="N28" s="1309">
-        <f>IFERROR(H28*M28,0)</f>
+      <c r="M28" s="509">
+        <f>IF(OR(F28="",F28=0),"",K28/F28)</f>
         <v/>
       </c>
+      <c r="N28" s="851" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="1223">
       <c r="A29" s="823" t="n"/>
@@ -11248,25 +11251,25 @@
       <c r="E29" s="848" t="n"/>
       <c r="F29" s="394" t="n"/>
       <c r="G29" s="394" t="n"/>
-      <c r="H29" s="394" t="n"/>
-      <c r="I29" s="216">
-        <f>IF(A29="","",G29+H29)</f>
+      <c r="H29" s="1310" t="n"/>
+      <c r="I29" s="1310">
+        <f>IFERROR(J29*H29,0)</f>
         <v/>
       </c>
-      <c r="J29" s="216">
-        <f>IF(F29="","",MAX(0,F29-I29))</f>
+      <c r="J29" s="394" t="n"/>
+      <c r="K29" s="216">
+        <f>IF(A29="","",G29+J29)</f>
         <v/>
       </c>
-      <c r="K29" s="509">
-        <f>IF(OR(F29="",F29=0),"",I29/F29)</f>
+      <c r="L29" s="216">
+        <f>IF(F29="","",MAX(0,F29-K29))</f>
         <v/>
       </c>
-      <c r="L29" s="814" t="n"/>
-      <c r="M29" s="1309" t="n"/>
-      <c r="N29" s="1309">
-        <f>IFERROR(H29*M29,0)</f>
+      <c r="M29" s="509">
+        <f>IF(OR(F29="",F29=0),"",K29/F29)</f>
         <v/>
       </c>
+      <c r="N29" s="851" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="1223">
       <c r="A30" s="823" t="n"/>
@@ -11276,25 +11279,25 @@
       <c r="E30" s="848" t="n"/>
       <c r="F30" s="394" t="n"/>
       <c r="G30" s="394" t="n"/>
-      <c r="H30" s="394" t="n"/>
-      <c r="I30" s="216">
-        <f>IF(A30="","",G30+H30)</f>
+      <c r="H30" s="1310" t="n"/>
+      <c r="I30" s="1310">
+        <f>IFERROR(J30*H30,0)</f>
         <v/>
       </c>
-      <c r="J30" s="216">
-        <f>IF(F30="","",MAX(0,F30-I30))</f>
+      <c r="J30" s="394" t="n"/>
+      <c r="K30" s="216">
+        <f>IF(A30="","",G30+J30)</f>
         <v/>
       </c>
-      <c r="K30" s="509">
-        <f>IF(OR(F30="",F30=0),"",I30/F30)</f>
+      <c r="L30" s="216">
+        <f>IF(F30="","",MAX(0,F30-K30))</f>
         <v/>
       </c>
-      <c r="L30" s="814" t="n"/>
-      <c r="M30" s="1309" t="n"/>
-      <c r="N30" s="1309">
-        <f>IFERROR(H30*M30,0)</f>
+      <c r="M30" s="509">
+        <f>IF(OR(F30="",F30=0),"",K30/F30)</f>
         <v/>
       </c>
+      <c r="N30" s="851" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="1223">
       <c r="A31" s="823" t="n"/>
@@ -11304,25 +11307,25 @@
       <c r="E31" s="848" t="n"/>
       <c r="F31" s="394" t="n"/>
       <c r="G31" s="394" t="n"/>
-      <c r="H31" s="394" t="n"/>
-      <c r="I31" s="216">
-        <f>IF(A31="","",G31+H31)</f>
+      <c r="H31" s="1310" t="n"/>
+      <c r="I31" s="1310">
+        <f>IFERROR(J31*H31,0)</f>
         <v/>
       </c>
-      <c r="J31" s="216">
-        <f>IF(F31="","",MAX(0,F31-I31))</f>
+      <c r="J31" s="394" t="n"/>
+      <c r="K31" s="216">
+        <f>IF(A31="","",G31+J31)</f>
         <v/>
       </c>
-      <c r="K31" s="509">
-        <f>IF(OR(F31="",F31=0),"",I31/F31)</f>
+      <c r="L31" s="216">
+        <f>IF(F31="","",MAX(0,F31-K31))</f>
         <v/>
       </c>
-      <c r="L31" s="814" t="n"/>
-      <c r="M31" s="1309" t="n"/>
-      <c r="N31" s="1309">
-        <f>IFERROR(H31*M31,0)</f>
+      <c r="M31" s="509">
+        <f>IF(OR(F31="",F31=0),"",K31/F31)</f>
         <v/>
       </c>
+      <c r="N31" s="851" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="1223">
       <c r="A32" s="823" t="n"/>
@@ -11332,25 +11335,25 @@
       <c r="E32" s="848" t="n"/>
       <c r="F32" s="394" t="n"/>
       <c r="G32" s="394" t="n"/>
-      <c r="H32" s="394" t="n"/>
-      <c r="I32" s="216">
-        <f>IF(A32="","",G32+H32)</f>
+      <c r="H32" s="1310" t="n"/>
+      <c r="I32" s="1310">
+        <f>IFERROR(J32*H32,0)</f>
         <v/>
       </c>
-      <c r="J32" s="216">
-        <f>IF(F32="","",MAX(0,F32-I32))</f>
+      <c r="J32" s="394" t="n"/>
+      <c r="K32" s="216">
+        <f>IF(A32="","",G32+J32)</f>
         <v/>
       </c>
-      <c r="K32" s="509">
-        <f>IF(OR(F32="",F32=0),"",I32/F32)</f>
+      <c r="L32" s="216">
+        <f>IF(F32="","",MAX(0,F32-K32))</f>
         <v/>
       </c>
-      <c r="L32" s="814" t="n"/>
-      <c r="M32" s="1309" t="n"/>
-      <c r="N32" s="1309">
-        <f>IFERROR(H32*M32,0)</f>
+      <c r="M32" s="509">
+        <f>IF(OR(F32="",F32=0),"",K32/F32)</f>
         <v/>
       </c>
+      <c r="N32" s="851" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="1223">
       <c r="A33" s="823" t="n"/>
@@ -11360,25 +11363,25 @@
       <c r="E33" s="848" t="n"/>
       <c r="F33" s="394" t="n"/>
       <c r="G33" s="394" t="n"/>
-      <c r="H33" s="394" t="n"/>
-      <c r="I33" s="216">
-        <f>IF(A33="","",G33+H33)</f>
+      <c r="H33" s="1310" t="n"/>
+      <c r="I33" s="1310">
+        <f>IFERROR(J33*H33,0)</f>
         <v/>
       </c>
-      <c r="J33" s="216">
-        <f>IF(F33="","",MAX(0,F33-I33))</f>
+      <c r="J33" s="394" t="n"/>
+      <c r="K33" s="216">
+        <f>IF(A33="","",G33+J33)</f>
         <v/>
       </c>
-      <c r="K33" s="509">
-        <f>IF(OR(F33="",F33=0),"",I33/F33)</f>
+      <c r="L33" s="216">
+        <f>IF(F33="","",MAX(0,F33-K33))</f>
         <v/>
       </c>
-      <c r="L33" s="814" t="n"/>
-      <c r="M33" s="1309" t="n"/>
-      <c r="N33" s="1309">
-        <f>IFERROR(H33*M33,0)</f>
+      <c r="M33" s="509">
+        <f>IF(OR(F33="",F33=0),"",K33/F33)</f>
         <v/>
       </c>
+      <c r="N33" s="851" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="1223" thickBot="1">
       <c r="A34" s="214" t="n"/>
@@ -11440,7 +11443,7 @@
       </c>
       <c r="J36" s="815" t="n"/>
       <c r="K36" s="511">
-        <f>SUM(N26:N33)</f>
+        <f>SUM(I26:I33)</f>
         <v/>
       </c>
       <c r="L36" s="889" t="inlineStr">

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -1689,7 +1689,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="411">
+  <borders count="412">
     <border>
       <left/>
       <right/>
@@ -6574,6 +6574,20 @@
       </top>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB8C2CC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB8C2CC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB8C2CC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB8C2CC"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="5">
@@ -6583,7 +6597,7 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1311">
+  <cellXfs count="1313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -9817,6 +9831,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="172" fontId="124" fillId="17" borderId="188" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="124" fillId="17" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="124" fillId="28" borderId="411" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="4">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11195,8 +11215,8 @@
       <c r="E27" s="848" t="n"/>
       <c r="F27" s="394" t="n"/>
       <c r="G27" s="394" t="n"/>
-      <c r="H27" s="1310" t="n"/>
-      <c r="I27" s="1310">
+      <c r="H27" s="1311" t="n"/>
+      <c r="I27" s="1311">
         <f>IFERROR(J27*H27,0)</f>
         <v/>
       </c>
@@ -11213,7 +11233,7 @@
         <f>IF(OR(F27="",F27=0),"",K27/F27)</f>
         <v/>
       </c>
-      <c r="N27" s="851" t="n"/>
+      <c r="N27" s="1312" t="n"/>
     </row>
     <row r="28" ht="18" customHeight="1" s="1223">
       <c r="A28" s="823" t="n"/>
@@ -11223,8 +11243,8 @@
       <c r="E28" s="848" t="n"/>
       <c r="F28" s="394" t="n"/>
       <c r="G28" s="394" t="n"/>
-      <c r="H28" s="1310" t="n"/>
-      <c r="I28" s="1310">
+      <c r="H28" s="1311" t="n"/>
+      <c r="I28" s="1311">
         <f>IFERROR(J28*H28,0)</f>
         <v/>
       </c>
@@ -11241,7 +11261,7 @@
         <f>IF(OR(F28="",F28=0),"",K28/F28)</f>
         <v/>
       </c>
-      <c r="N28" s="851" t="n"/>
+      <c r="N28" s="1312" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1" s="1223">
       <c r="A29" s="823" t="n"/>
@@ -11251,8 +11271,8 @@
       <c r="E29" s="848" t="n"/>
       <c r="F29" s="394" t="n"/>
       <c r="G29" s="394" t="n"/>
-      <c r="H29" s="1310" t="n"/>
-      <c r="I29" s="1310">
+      <c r="H29" s="1311" t="n"/>
+      <c r="I29" s="1311">
         <f>IFERROR(J29*H29,0)</f>
         <v/>
       </c>
@@ -11269,7 +11289,7 @@
         <f>IF(OR(F29="",F29=0),"",K29/F29)</f>
         <v/>
       </c>
-      <c r="N29" s="851" t="n"/>
+      <c r="N29" s="1312" t="n"/>
     </row>
     <row r="30" ht="18" customHeight="1" s="1223">
       <c r="A30" s="823" t="n"/>
@@ -11279,8 +11299,8 @@
       <c r="E30" s="848" t="n"/>
       <c r="F30" s="394" t="n"/>
       <c r="G30" s="394" t="n"/>
-      <c r="H30" s="1310" t="n"/>
-      <c r="I30" s="1310">
+      <c r="H30" s="1311" t="n"/>
+      <c r="I30" s="1311">
         <f>IFERROR(J30*H30,0)</f>
         <v/>
       </c>
@@ -11297,7 +11317,7 @@
         <f>IF(OR(F30="",F30=0),"",K30/F30)</f>
         <v/>
       </c>
-      <c r="N30" s="851" t="n"/>
+      <c r="N30" s="1312" t="n"/>
     </row>
     <row r="31" ht="18" customHeight="1" s="1223">
       <c r="A31" s="823" t="n"/>
@@ -11307,8 +11327,8 @@
       <c r="E31" s="848" t="n"/>
       <c r="F31" s="394" t="n"/>
       <c r="G31" s="394" t="n"/>
-      <c r="H31" s="1310" t="n"/>
-      <c r="I31" s="1310">
+      <c r="H31" s="1311" t="n"/>
+      <c r="I31" s="1311">
         <f>IFERROR(J31*H31,0)</f>
         <v/>
       </c>
@@ -11325,7 +11345,7 @@
         <f>IF(OR(F31="",F31=0),"",K31/F31)</f>
         <v/>
       </c>
-      <c r="N31" s="851" t="n"/>
+      <c r="N31" s="1312" t="n"/>
     </row>
     <row r="32" ht="18" customHeight="1" s="1223">
       <c r="A32" s="823" t="n"/>
@@ -11335,8 +11355,8 @@
       <c r="E32" s="848" t="n"/>
       <c r="F32" s="394" t="n"/>
       <c r="G32" s="394" t="n"/>
-      <c r="H32" s="1310" t="n"/>
-      <c r="I32" s="1310">
+      <c r="H32" s="1311" t="n"/>
+      <c r="I32" s="1311">
         <f>IFERROR(J32*H32,0)</f>
         <v/>
       </c>
@@ -11353,7 +11373,7 @@
         <f>IF(OR(F32="",F32=0),"",K32/F32)</f>
         <v/>
       </c>
-      <c r="N32" s="851" t="n"/>
+      <c r="N32" s="1312" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1" s="1223">
       <c r="A33" s="823" t="n"/>
@@ -11363,8 +11383,8 @@
       <c r="E33" s="848" t="n"/>
       <c r="F33" s="394" t="n"/>
       <c r="G33" s="394" t="n"/>
-      <c r="H33" s="1310" t="n"/>
-      <c r="I33" s="1310">
+      <c r="H33" s="1311" t="n"/>
+      <c r="I33" s="1311">
         <f>IFERROR(J33*H33,0)</f>
         <v/>
       </c>
@@ -11381,7 +11401,7 @@
         <f>IF(OR(F33="",F33=0),"",K33/F33)</f>
         <v/>
       </c>
-      <c r="N33" s="851" t="n"/>
+      <c r="N33" s="1312" t="n"/>
     </row>
     <row r="34" ht="18" customHeight="1" s="1223" thickBot="1">
       <c r="A34" s="214" t="n"/>

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -11145,17 +11145,17 @@
       </c>
       <c r="H25" s="830" t="inlineStr">
         <is>
+          <t>Cant. acta</t>
+        </is>
+      </c>
+      <c r="I25" s="830" t="inlineStr">
+        <is>
           <t>Precio unitario</t>
         </is>
       </c>
-      <c r="I25" s="830" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
       <c r="J25" s="830" t="inlineStr">
         <is>
-          <t>Cant. acta</t>
+          <t>Valor esta acta</t>
         </is>
       </c>
       <c r="K25" s="830" t="inlineStr">
@@ -11187,14 +11187,14 @@
       <c r="E26" s="392" t="n"/>
       <c r="F26" s="393" t="n"/>
       <c r="G26" s="393" t="n"/>
-      <c r="H26" s="1310" t="n"/>
-      <c r="I26" s="1310">
-        <f>IFERROR(J26*H26,0)</f>
+      <c r="H26" s="393" t="n"/>
+      <c r="I26" s="1310" t="n"/>
+      <c r="J26" s="1310">
+        <f>IFERROR(H26*I26,0)</f>
         <v/>
       </c>
-      <c r="J26" s="393" t="n"/>
       <c r="K26" s="215">
-        <f>IF(A26="","",G26+J26)</f>
+        <f>IF(A26="","",G26+H26)</f>
         <v/>
       </c>
       <c r="L26" s="215">
@@ -11215,14 +11215,14 @@
       <c r="E27" s="848" t="n"/>
       <c r="F27" s="394" t="n"/>
       <c r="G27" s="394" t="n"/>
-      <c r="H27" s="1311" t="n"/>
-      <c r="I27" s="1311">
-        <f>IFERROR(J27*H27,0)</f>
+      <c r="H27" s="394" t="n"/>
+      <c r="I27" s="1311" t="n"/>
+      <c r="J27" s="1311">
+        <f>IFERROR(H27*I27,0)</f>
         <v/>
       </c>
-      <c r="J27" s="394" t="n"/>
       <c r="K27" s="216">
-        <f>IF(A27="","",G27+J27)</f>
+        <f>IF(A27="","",G27+H27)</f>
         <v/>
       </c>
       <c r="L27" s="216">
@@ -11243,14 +11243,14 @@
       <c r="E28" s="848" t="n"/>
       <c r="F28" s="394" t="n"/>
       <c r="G28" s="394" t="n"/>
-      <c r="H28" s="1311" t="n"/>
-      <c r="I28" s="1311">
-        <f>IFERROR(J28*H28,0)</f>
+      <c r="H28" s="394" t="n"/>
+      <c r="I28" s="1311" t="n"/>
+      <c r="J28" s="1311">
+        <f>IFERROR(H28*I28,0)</f>
         <v/>
       </c>
-      <c r="J28" s="394" t="n"/>
       <c r="K28" s="216">
-        <f>IF(A28="","",G28+J28)</f>
+        <f>IF(A28="","",G28+H28)</f>
         <v/>
       </c>
       <c r="L28" s="216">
@@ -11271,14 +11271,14 @@
       <c r="E29" s="848" t="n"/>
       <c r="F29" s="394" t="n"/>
       <c r="G29" s="394" t="n"/>
-      <c r="H29" s="1311" t="n"/>
-      <c r="I29" s="1311">
-        <f>IFERROR(J29*H29,0)</f>
+      <c r="H29" s="394" t="n"/>
+      <c r="I29" s="1311" t="n"/>
+      <c r="J29" s="1311">
+        <f>IFERROR(H29*I29,0)</f>
         <v/>
       </c>
-      <c r="J29" s="394" t="n"/>
       <c r="K29" s="216">
-        <f>IF(A29="","",G29+J29)</f>
+        <f>IF(A29="","",G29+H29)</f>
         <v/>
       </c>
       <c r="L29" s="216">
@@ -11299,14 +11299,14 @@
       <c r="E30" s="848" t="n"/>
       <c r="F30" s="394" t="n"/>
       <c r="G30" s="394" t="n"/>
-      <c r="H30" s="1311" t="n"/>
-      <c r="I30" s="1311">
-        <f>IFERROR(J30*H30,0)</f>
+      <c r="H30" s="394" t="n"/>
+      <c r="I30" s="1311" t="n"/>
+      <c r="J30" s="1311">
+        <f>IFERROR(H30*I30,0)</f>
         <v/>
       </c>
-      <c r="J30" s="394" t="n"/>
       <c r="K30" s="216">
-        <f>IF(A30="","",G30+J30)</f>
+        <f>IF(A30="","",G30+H30)</f>
         <v/>
       </c>
       <c r="L30" s="216">
@@ -11327,14 +11327,14 @@
       <c r="E31" s="848" t="n"/>
       <c r="F31" s="394" t="n"/>
       <c r="G31" s="394" t="n"/>
-      <c r="H31" s="1311" t="n"/>
-      <c r="I31" s="1311">
-        <f>IFERROR(J31*H31,0)</f>
+      <c r="H31" s="394" t="n"/>
+      <c r="I31" s="1311" t="n"/>
+      <c r="J31" s="1311">
+        <f>IFERROR(H31*I31,0)</f>
         <v/>
       </c>
-      <c r="J31" s="394" t="n"/>
       <c r="K31" s="216">
-        <f>IF(A31="","",G31+J31)</f>
+        <f>IF(A31="","",G31+H31)</f>
         <v/>
       </c>
       <c r="L31" s="216">
@@ -11355,14 +11355,14 @@
       <c r="E32" s="848" t="n"/>
       <c r="F32" s="394" t="n"/>
       <c r="G32" s="394" t="n"/>
-      <c r="H32" s="1311" t="n"/>
-      <c r="I32" s="1311">
-        <f>IFERROR(J32*H32,0)</f>
+      <c r="H32" s="394" t="n"/>
+      <c r="I32" s="1311" t="n"/>
+      <c r="J32" s="1311">
+        <f>IFERROR(H32*I32,0)</f>
         <v/>
       </c>
-      <c r="J32" s="394" t="n"/>
       <c r="K32" s="216">
-        <f>IF(A32="","",G32+J32)</f>
+        <f>IF(A32="","",G32+H32)</f>
         <v/>
       </c>
       <c r="L32" s="216">
@@ -11383,14 +11383,14 @@
       <c r="E33" s="848" t="n"/>
       <c r="F33" s="394" t="n"/>
       <c r="G33" s="394" t="n"/>
-      <c r="H33" s="1311" t="n"/>
-      <c r="I33" s="1311">
-        <f>IFERROR(J33*H33,0)</f>
+      <c r="H33" s="394" t="n"/>
+      <c r="I33" s="1311" t="n"/>
+      <c r="J33" s="1311">
+        <f>IFERROR(H33*I33,0)</f>
         <v/>
       </c>
-      <c r="J33" s="394" t="n"/>
       <c r="K33" s="216">
-        <f>IF(A33="","",G33+J33)</f>
+        <f>IF(A33="","",G33+H33)</f>
         <v/>
       </c>
       <c r="L33" s="216">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="J36" s="815" t="n"/>
       <c r="K36" s="511">
-        <f>SUM(I26:I33)</f>
+        <f>SUM(J26:J33)</f>
         <v/>
       </c>
       <c r="L36" s="889" t="inlineStr">

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -10654,7 +10654,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N88"/>

--- a/public/plantilla-acta.xlsx
+++ b/public/plantilla-acta.xlsx
@@ -10403,31 +10403,6 @@
 </chartSpace>
 </file>
 
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>OpenAI</author>
-  </authors>
-  <commentList>
-    <comment ref="I26" authorId="0" shapeId="0">
-      <text>
-        <t>Cantidad acumulada = cantidad anterior + cantidad del presente acta.</t>
-      </text>
-    </comment>
-    <comment ref="J26" authorId="0" shapeId="0">
-      <text>
-        <t>Saldo = cantidad contractual - cantidad acumulada. No permite saldos negativos.</t>
-      </text>
-    </comment>
-    <comment ref="K26" authorId="0" shapeId="0">
-      <text>
-        <t>% ejecución = cantidad acumulada / cantidad contractual.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -12569,6 +12544,5 @@
     <firstFooter/>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>